--- a/design/tables/Goods.xlsx
+++ b/design/tables/Goods.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Goods" sheetId="1" r:id="R8bec8cc149d34239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Goods" sheetId="1" r:id="R1ca20cd68d494cbe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -417,7 +417,7 @@
         <x:v>goods.cola.story</x:v>
       </x:c>
       <x:c r="H6" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
@@ -469,7 +469,7 @@
         <x:v>goods.noodles.story</x:v>
       </x:c>
       <x:c r="H8" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -521,7 +521,7 @@
         <x:v>goods.chips.story</x:v>
       </x:c>
       <x:c r="H10" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
@@ -547,7 +547,7 @@
         <x:v>goods.cookies.story</x:v>
       </x:c>
       <x:c r="H11" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
@@ -573,7 +573,7 @@
         <x:v>goods.jelly.story</x:v>
       </x:c>
       <x:c r="H12" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
@@ -599,7 +599,7 @@
         <x:v>goods.water.story</x:v>
       </x:c>
       <x:c r="H13" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
@@ -625,7 +625,7 @@
         <x:v>goods.rice.story</x:v>
       </x:c>
       <x:c r="H14" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
